--- a/Products Price table Web.xlsx
+++ b/Products Price table Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1EB26E-2B26-4937-9484-40CB46C73899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70A3C6B-2995-402C-B50B-E063C45F76E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="124">
   <si>
     <t>Items</t>
   </si>
@@ -427,8 +427,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.000"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -748,7 +749,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -980,9 +981,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1031,6 +1029,48 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1372,10 +1412,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="18.75">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="80" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="79" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -1741,7 +1781,7 @@
       <c r="A8" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="81" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -1794,7 +1834,7 @@
       <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="82" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -1876,8 +1916,8 @@
       <c r="K10" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="27"/>
-      <c r="M10" s="25"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="96"/>
       <c r="N10" s="27">
         <v>95.4</v>
       </c>
@@ -1894,38 +1934,41 @@
       <c r="B11" s="77" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="106">
         <v>20</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="107">
         <f>F11*42</f>
         <v>840</v>
       </c>
-      <c r="H11" s="25">
-        <v>42</v>
-      </c>
-      <c r="I11" s="25"/>
-      <c r="J11" s="27">
+      <c r="H11" s="106">
+        <v>42</v>
+      </c>
+      <c r="I11" s="106">
+        <v>3.18</v>
+      </c>
+      <c r="J11" s="109">
         <v>4.875</v>
       </c>
-      <c r="K11" s="77" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="27"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="27">
+      <c r="K11" s="75">
+        <f t="shared" si="1"/>
+        <v>0.53301886792452824</v>
+      </c>
+      <c r="L11" s="46"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="108">
         <v>97.5</v>
       </c>
-      <c r="O11" s="27"/>
+      <c r="O11" s="108"/>
       <c r="P11" s="28" t="s">
         <v>32</v>
       </c>
@@ -1938,7 +1981,7 @@
       <c r="B12" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="86" t="s">
+      <c r="C12" s="85" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="77" t="s">
@@ -1960,7 +2003,7 @@
       <c r="I12" s="77">
         <v>2.87</v>
       </c>
-      <c r="J12" s="84">
+      <c r="J12" s="83">
         <f>N12/F12</f>
         <v>4.5999999999999996</v>
       </c>
@@ -1968,9 +2011,9 @@
         <f t="shared" si="1"/>
         <v>0.60278745644599274</v>
       </c>
-      <c r="L12" s="31"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="84">
+      <c r="L12" s="32"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="83">
         <v>92</v>
       </c>
       <c r="O12" s="32"/>
@@ -1985,7 +2028,7 @@
       <c r="B13" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="85" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="77" t="s">
@@ -2007,7 +2050,7 @@
       <c r="I13" s="77">
         <v>2.87</v>
       </c>
-      <c r="J13" s="84">
+      <c r="J13" s="83">
         <f>N13/F13</f>
         <v>0</v>
       </c>
@@ -2015,9 +2058,9 @@
         <f>J12/I12-1</f>
         <v>0.60278745644599274</v>
       </c>
-      <c r="L13" s="34"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="85"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="98"/>
+      <c r="N13" s="84"/>
       <c r="O13" s="35"/>
       <c r="P13" s="28" t="s">
         <v>32</v>
@@ -2060,8 +2103,8 @@
         <f t="shared" si="1"/>
         <v>0.56794425087108014</v>
       </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="10"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="99"/>
       <c r="N14" s="9">
         <v>90</v>
       </c>
@@ -2107,8 +2150,8 @@
         <f>J15/I14-1</f>
         <v>0.88153310104529625</v>
       </c>
-      <c r="L15" s="9"/>
-      <c r="M15" s="10"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="99"/>
       <c r="N15" s="9">
         <v>108</v>
       </c>
@@ -2124,7 +2167,7 @@
       <c r="B16" s="77" t="s">
         <v>117</v>
       </c>
-      <c r="C16" s="86" t="s">
+      <c r="C16" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D16" s="77" t="s">
@@ -2154,8 +2197,8 @@
         <f t="shared" si="1"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="10"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="99"/>
       <c r="N16" s="9">
         <v>79.5</v>
       </c>
@@ -2171,7 +2214,7 @@
       <c r="B17" s="77" t="s">
         <v>117</v>
       </c>
-      <c r="C17" s="86" t="s">
+      <c r="C17" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D17" s="77" t="s">
@@ -2193,7 +2236,7 @@
       <c r="I17" s="77">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J17" s="84">
+      <c r="J17" s="83">
         <f>N17/F16</f>
         <v>4.6500000000000004</v>
       </c>
@@ -2201,9 +2244,9 @@
         <f>J17/I16-1</f>
         <v>0.5</v>
       </c>
-      <c r="L17" s="84"/>
-      <c r="M17" s="77"/>
-      <c r="N17" s="84">
+      <c r="L17" s="100"/>
+      <c r="M17" s="101"/>
+      <c r="N17" s="83">
         <v>69.75</v>
       </c>
       <c r="O17" s="11"/>
@@ -2218,7 +2261,7 @@
       <c r="B18" s="77" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="86" t="s">
+      <c r="C18" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="77" t="s">
@@ -2240,7 +2283,7 @@
       <c r="I18" s="77">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J18" s="84">
+      <c r="J18" s="83">
         <f>N18/F17</f>
         <v>4.7166666666666668</v>
       </c>
@@ -2248,9 +2291,9 @@
         <f>J17/I16-1</f>
         <v>0.5</v>
       </c>
-      <c r="L18" s="85"/>
-      <c r="M18" s="79"/>
-      <c r="N18" s="84">
+      <c r="L18" s="102"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="83">
         <v>70.75</v>
       </c>
       <c r="O18" s="11"/>
@@ -2265,7 +2308,7 @@
       <c r="B19" s="77" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="86" t="s">
+      <c r="C19" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="13" t="s">
@@ -2313,10 +2356,10 @@
       <c r="A20" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="83" t="s">
+      <c r="B20" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="86" t="s">
+      <c r="C20" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="77" t="s">
@@ -2360,10 +2403,10 @@
       <c r="A21" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="83" t="s">
+      <c r="B21" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="86" t="s">
+      <c r="C21" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="77" t="s">
@@ -2385,7 +2428,7 @@
       <c r="I21" s="77">
         <v>4.92</v>
       </c>
-      <c r="J21" s="84">
+      <c r="J21" s="83">
         <f>N21/F$20</f>
         <v>5.6</v>
       </c>
@@ -2395,7 +2438,7 @@
       </c>
       <c r="L21" s="31"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="84">
+      <c r="N21" s="83">
         <v>112</v>
       </c>
       <c r="O21" s="11"/>
@@ -2407,10 +2450,10 @@
       <c r="A22" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="86" t="s">
+      <c r="C22" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D22" s="77" t="s">
@@ -2432,7 +2475,7 @@
       <c r="I22" s="77">
         <v>5.92</v>
       </c>
-      <c r="J22" s="84">
+      <c r="J22" s="83">
         <f>N22/F$20</f>
         <v>0</v>
       </c>
@@ -2442,7 +2485,7 @@
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="14"/>
-      <c r="N22" s="85"/>
+      <c r="N22" s="84"/>
       <c r="O22" s="11"/>
       <c r="P22" s="28" t="s">
         <v>32</v>
@@ -2452,10 +2495,10 @@
       <c r="A23" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="86" t="s">
+      <c r="C23" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D23" s="77" t="s">
@@ -2499,10 +2542,10 @@
       <c r="A24" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="83" t="s">
+      <c r="B24" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="86" t="s">
+      <c r="C24" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D24" s="10" t="s">
@@ -2552,7 +2595,7 @@
       <c r="A25" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="81" t="s">
         <v>45</v>
       </c>
       <c r="C25" s="37" t="s">
@@ -2787,10 +2830,10 @@
       <c r="A30" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="91" t="s">
+      <c r="B30" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="86" t="s">
+      <c r="C30" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="77" t="s">
@@ -2834,10 +2877,10 @@
       <c r="A31" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="91" t="s">
+      <c r="B31" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="86" t="s">
+      <c r="C31" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="77" t="s">
@@ -2881,10 +2924,10 @@
       <c r="A32" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="91" t="s">
+      <c r="B32" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="86" t="s">
+      <c r="C32" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D32" s="77" t="s">
@@ -2928,10 +2971,10 @@
       <c r="A33" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="91" t="s">
+      <c r="B33" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="86" t="s">
+      <c r="C33" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D33" s="77" t="s">
@@ -2975,10 +3018,10 @@
       <c r="A34" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="91" t="s">
+      <c r="B34" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="86" t="s">
+      <c r="C34" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D34" s="77" t="s">
@@ -3022,10 +3065,10 @@
       <c r="A35" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="91" t="s">
+      <c r="B35" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="86" t="s">
+      <c r="C35" s="85" t="s">
         <v>39</v>
       </c>
       <c r="D35" s="77" t="s">
@@ -3066,10 +3109,10 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A36" s="83" t="s">
+      <c r="A36" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="88" t="s">
+      <c r="B36" s="87" t="s">
         <v>54</v>
       </c>
       <c r="C36" s="10" t="s">
@@ -3116,8 +3159,8 @@
       </c>
     </row>
     <row r="37" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A37" s="83"/>
-      <c r="B37" s="88" t="s">
+      <c r="A37" s="82"/>
+      <c r="B37" s="87" t="s">
         <v>57</v>
       </c>
       <c r="C37" s="10" t="s">
@@ -3167,13 +3210,13 @@
       <c r="A38" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="89" t="s">
+      <c r="B38" s="88" t="s">
         <v>60</v>
       </c>
       <c r="C38" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="93" t="s">
+      <c r="D38" s="92" t="s">
         <v>61</v>
       </c>
       <c r="E38" s="77" t="s">
@@ -3214,13 +3257,13 @@
       <c r="A39" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="89" t="s">
+      <c r="B39" s="88" t="s">
         <v>60</v>
       </c>
       <c r="C39" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="93" t="s">
+      <c r="D39" s="92" t="s">
         <v>61</v>
       </c>
       <c r="E39" s="77" t="s">
@@ -3261,7 +3304,7 @@
       <c r="A40" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="89" t="s">
+      <c r="B40" s="88" t="s">
         <v>63</v>
       </c>
       <c r="C40" s="7" t="s">
@@ -3315,7 +3358,7 @@
       <c r="A41" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B41" s="94" t="s">
+      <c r="B41" s="93" t="s">
         <v>66</v>
       </c>
       <c r="C41" s="48" t="s">
@@ -3358,7 +3401,7 @@
       <c r="A42" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="90" t="s">
+      <c r="B42" s="89" t="s">
         <v>68</v>
       </c>
       <c r="C42" s="54" t="s">
@@ -3397,10 +3440,10 @@
       <c r="A43" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="82" t="s">
+      <c r="B43" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="86" t="s">
+      <c r="C43" s="85" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="10" t="s">
@@ -3449,10 +3492,10 @@
       <c r="A44" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="82" t="s">
+      <c r="B44" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="86" t="s">
+      <c r="C44" s="85" t="s">
         <v>72</v>
       </c>
       <c r="D44" s="16" t="s">
@@ -3502,7 +3545,7 @@
       <c r="A45" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="92" t="s">
+      <c r="B45" s="91" t="s">
         <v>78</v>
       </c>
       <c r="C45" s="30" t="s">
@@ -3555,7 +3598,7 @@
       <c r="A46" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="92" t="s">
+      <c r="B46" s="91" t="s">
         <v>80</v>
       </c>
       <c r="C46" s="30" t="s">
@@ -3607,7 +3650,7 @@
       <c r="A47" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B47" s="92" t="s">
+      <c r="B47" s="91" t="s">
         <v>83</v>
       </c>
       <c r="C47" s="30" t="s">
@@ -3635,7 +3678,7 @@
       <c r="A48" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B48" s="95" t="s">
+      <c r="B48" s="94" t="s">
         <v>86</v>
       </c>
       <c r="C48" s="77" t="s">
@@ -3685,7 +3728,7 @@
       <c r="A49" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="95" t="s">
+      <c r="B49" s="94" t="s">
         <v>90</v>
       </c>
       <c r="C49" s="77" t="s">
@@ -3735,7 +3778,7 @@
       <c r="A50" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B50" s="95" t="s">
+      <c r="B50" s="94" t="s">
         <v>92</v>
       </c>
       <c r="C50" s="77" t="s">
@@ -3785,7 +3828,7 @@
       <c r="A51" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B51" s="95" t="s">
+      <c r="B51" s="94" t="s">
         <v>94</v>
       </c>
       <c r="C51" s="77" t="s">
@@ -3834,7 +3877,7 @@
       <c r="A52" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B52" s="95" t="s">
+      <c r="B52" s="94" t="s">
         <v>96</v>
       </c>
       <c r="C52" s="77" t="s">
@@ -3884,7 +3927,7 @@
       <c r="A53" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B53" s="95" t="s">
+      <c r="B53" s="94" t="s">
         <v>98</v>
       </c>
       <c r="C53" s="77" t="s">
@@ -3934,7 +3977,7 @@
       <c r="A54" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="95" t="s">
+      <c r="B54" s="94" t="s">
         <v>100</v>
       </c>
       <c r="C54" s="77" t="s">
@@ -3984,10 +4027,10 @@
       <c r="A55" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B55" s="95" t="s">
+      <c r="B55" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="86" t="s">
+      <c r="C55" s="85" t="s">
         <v>119</v>
       </c>
       <c r="D55" s="70" t="s">
@@ -4034,10 +4077,10 @@
       <c r="A56" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B56" s="95" t="s">
+      <c r="B56" s="94" t="s">
         <v>104</v>
       </c>
-      <c r="C56" s="86" t="s">
+      <c r="C56" s="85" t="s">
         <v>119</v>
       </c>
       <c r="D56" s="70" t="s">
@@ -4084,10 +4127,10 @@
       <c r="A57" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B57" s="96" t="s">
+      <c r="B57" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="C57" s="86" t="s">
+      <c r="C57" s="85" t="s">
         <v>119</v>
       </c>
       <c r="D57" s="70" t="s">
@@ -4133,10 +4176,10 @@
       <c r="A58" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B58" s="95" t="s">
+      <c r="B58" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="C58" s="86" t="s">
+      <c r="C58" s="85" t="s">
         <v>109</v>
       </c>
       <c r="D58" s="70" t="s">
@@ -4183,10 +4226,10 @@
       <c r="A59" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B59" s="95" t="s">
+      <c r="B59" s="94" t="s">
         <v>111</v>
       </c>
-      <c r="C59" s="87"/>
+      <c r="C59" s="86"/>
       <c r="D59" s="70" t="s">
         <v>112</v>
       </c>

--- a/Products Price table Web.xlsx
+++ b/Products Price table Web.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70A3C6B-2995-402C-B50B-E063C45F76E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6622B38C-84F4-45E0-BB73-C53FDF1BF103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
   </bookViews>
   <sheets>
     <sheet name="Item Classification 7.14.26" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="123">
   <si>
     <t>Items</t>
   </si>
@@ -273,9 +273,6 @@
     <t>BBR0001</t>
   </si>
   <si>
-    <t>1:30 ratio</t>
-  </si>
-  <si>
     <t>Beef Leg Bone Broth 15</t>
   </si>
   <si>
@@ -420,7 +417,7 @@
     <t>margin ratio(%)</t>
   </si>
   <si>
-    <t>1:15 ratio; Wooltari</t>
+    <t>9 Star</t>
   </si>
 </sst>
 </file>
@@ -749,7 +746,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -978,9 +975,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -995,15 +989,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1018,9 +1003,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1042,35 +1024,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1396,7 +1354,7 @@
   <cols>
     <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="39.140625" customWidth="1"/>
-    <col min="3" max="3" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" style="1" customWidth="1"/>
     <col min="4" max="5" width="11.5703125" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="1"/>
     <col min="7" max="7" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1412,10 +1370,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="18.75">
-      <c r="A1" s="80" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="79" t="s">
+      <c r="A1" s="79" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="78" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -1437,13 +1395,13 @@
         <v>6</v>
       </c>
       <c r="I1" s="73" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="74" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>8</v>
@@ -1468,26 +1426,26 @@
       <c r="B2" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="77">
+      <c r="E2" s="7">
         <v>5</v>
       </c>
-      <c r="F2" s="77">
+      <c r="F2" s="7">
         <v>25</v>
       </c>
-      <c r="G2" s="77">
+      <c r="G2" s="7">
         <f t="shared" ref="G2:G7" si="0">F2*42</f>
         <v>1050</v>
       </c>
-      <c r="H2" s="77">
-        <v>42</v>
-      </c>
-      <c r="I2" s="77">
+      <c r="H2" s="7">
+        <v>42</v>
+      </c>
+      <c r="I2" s="7">
         <v>2.95</v>
       </c>
       <c r="J2" s="9">
@@ -1520,26 +1478,26 @@
       <c r="B3" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="77">
+      <c r="E3" s="7">
         <v>5</v>
       </c>
-      <c r="F3" s="77">
+      <c r="F3" s="7">
         <v>25</v>
       </c>
-      <c r="G3" s="77">
+      <c r="G3" s="7">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="H3" s="77">
+      <c r="H3" s="7">
         <v>43</v>
       </c>
-      <c r="I3" s="77">
+      <c r="I3" s="7">
         <v>3.95</v>
       </c>
       <c r="J3" s="9">
@@ -1572,7 +1530,7 @@
       <c r="B4" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="77" t="s">
+      <c r="C4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="10" t="s">
@@ -1588,7 +1546,7 @@
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
-      <c r="H4" s="77">
+      <c r="H4" s="7">
         <v>44</v>
       </c>
       <c r="I4" s="10">
@@ -1626,26 +1584,26 @@
       <c r="B5" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="77" t="s">
+      <c r="C5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="77">
+      <c r="E5" s="7">
         <v>5</v>
       </c>
-      <c r="F5" s="77">
+      <c r="F5" s="7">
         <v>25</v>
       </c>
-      <c r="G5" s="77">
+      <c r="G5" s="7">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="H5" s="77">
-        <v>42</v>
-      </c>
-      <c r="I5" s="77">
+      <c r="H5" s="7">
+        <v>42</v>
+      </c>
+      <c r="I5" s="7">
         <v>2.86</v>
       </c>
       <c r="J5" s="9">
@@ -1678,26 +1636,26 @@
       <c r="B6" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="77" t="s">
+      <c r="C6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="77">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="77">
+      <c r="F6" s="7">
         <v>25</v>
       </c>
-      <c r="G6" s="77">
+      <c r="G6" s="7">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="H6" s="77">
-        <v>42</v>
-      </c>
-      <c r="I6" s="77">
+      <c r="H6" s="7">
+        <v>42</v>
+      </c>
+      <c r="I6" s="7">
         <v>2.86</v>
       </c>
       <c r="J6" s="9">
@@ -1730,7 +1688,7 @@
       <c r="B7" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="77" t="s">
+      <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="10" t="s">
@@ -1781,7 +1739,7 @@
       <c r="A8" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="81" t="s">
+      <c r="B8" s="80" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -1803,14 +1761,14 @@
       <c r="H8" s="10">
         <v>42</v>
       </c>
-      <c r="I8" s="77" t="s">
+      <c r="I8" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J8" s="9">
         <f>N8/F8</f>
         <v>5.2</v>
       </c>
-      <c r="K8" s="77" t="s">
+      <c r="K8" s="7" t="s">
         <v>34</v>
       </c>
       <c r="L8" s="9">
@@ -1834,7 +1792,7 @@
       <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="81" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -1888,7 +1846,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>28</v>
@@ -1913,11 +1871,11 @@
       <c r="J10" s="27">
         <v>5.3</v>
       </c>
-      <c r="K10" s="77" t="s">
+      <c r="K10" s="7" t="s">
         <v>34</v>
       </c>
       <c r="L10" s="46"/>
-      <c r="M10" s="96"/>
+      <c r="M10" s="91"/>
       <c r="N10" s="27">
         <v>95.4</v>
       </c>
@@ -1932,31 +1890,31 @@
         <v>30</v>
       </c>
       <c r="B11" s="77" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="104" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="105" t="s">
+      <c r="D11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="105" t="s">
+      <c r="E11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="106">
+      <c r="F11" s="20">
         <v>20</v>
       </c>
-      <c r="G11" s="107">
+      <c r="G11" s="19">
         <f>F11*42</f>
         <v>840</v>
       </c>
-      <c r="H11" s="106">
-        <v>42</v>
-      </c>
-      <c r="I11" s="106">
+      <c r="H11" s="20">
+        <v>42</v>
+      </c>
+      <c r="I11" s="20">
         <v>3.18</v>
       </c>
-      <c r="J11" s="109">
+      <c r="J11" s="95">
         <v>4.875</v>
       </c>
       <c r="K11" s="75">
@@ -1964,11 +1922,11 @@
         <v>0.53301886792452824</v>
       </c>
       <c r="L11" s="46"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="108">
+      <c r="M11" s="91"/>
+      <c r="N11" s="21">
         <v>97.5</v>
       </c>
-      <c r="O11" s="108"/>
+      <c r="O11" s="21"/>
       <c r="P11" s="28" t="s">
         <v>32</v>
       </c>
@@ -1979,31 +1937,31 @@
         <v>30</v>
       </c>
       <c r="B12" s="77" t="s">
-        <v>115</v>
-      </c>
-      <c r="C12" s="85" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="77" t="s">
+      <c r="D12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="77" t="s">
+      <c r="E12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="77">
+      <c r="F12" s="7">
         <v>20</v>
       </c>
-      <c r="G12" s="77">
+      <c r="G12" s="7">
         <f t="shared" si="2"/>
         <v>840</v>
       </c>
       <c r="H12" s="10">
         <v>42</v>
       </c>
-      <c r="I12" s="77">
+      <c r="I12" s="7">
         <v>2.87</v>
       </c>
-      <c r="J12" s="83">
+      <c r="J12" s="31">
         <f>N12/F12</f>
         <v>4.5999999999999996</v>
       </c>
@@ -2012,8 +1970,8 @@
         <v>0.60278745644599274</v>
       </c>
       <c r="L12" s="32"/>
-      <c r="M12" s="97"/>
-      <c r="N12" s="83">
+      <c r="M12" s="92"/>
+      <c r="N12" s="82">
         <v>92</v>
       </c>
       <c r="O12" s="32"/>
@@ -2026,41 +1984,43 @@
         <v>30</v>
       </c>
       <c r="B13" s="77" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="85" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="77" t="s">
+      <c r="D13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="77" t="s">
+      <c r="E13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="77">
+      <c r="F13" s="7">
         <v>20</v>
       </c>
-      <c r="G13" s="77">
+      <c r="G13" s="7">
         <f t="shared" ref="G13" si="3">F13*42</f>
         <v>840</v>
       </c>
       <c r="H13" s="13">
         <v>42</v>
       </c>
-      <c r="I13" s="77">
+      <c r="I13" s="7">
         <v>2.87</v>
       </c>
-      <c r="J13" s="83">
+      <c r="J13" s="31">
         <f>N13/F13</f>
-        <v>0</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="K13" s="75">
         <f>J12/I12-1</f>
         <v>0.60278745644599274</v>
       </c>
       <c r="L13" s="35"/>
-      <c r="M13" s="98"/>
-      <c r="N13" s="84"/>
+      <c r="M13" s="93"/>
+      <c r="N13" s="82">
+        <v>92</v>
+      </c>
       <c r="O13" s="35"/>
       <c r="P13" s="28" t="s">
         <v>32</v>
@@ -2071,28 +2031,28 @@
         <v>30</v>
       </c>
       <c r="B14" s="77" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="77" t="s">
+      <c r="D14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="77" t="s">
+      <c r="E14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="77">
+      <c r="F14" s="7">
         <v>20</v>
       </c>
-      <c r="G14" s="77">
+      <c r="G14" s="7">
         <f t="shared" si="2"/>
         <v>840</v>
       </c>
-      <c r="H14" s="77">
-        <v>42</v>
-      </c>
-      <c r="I14" s="77">
+      <c r="H14" s="7">
+        <v>42</v>
+      </c>
+      <c r="I14" s="7">
         <v>2.87</v>
       </c>
       <c r="J14" s="9">
@@ -2104,7 +2064,7 @@
         <v>0.56794425087108014</v>
       </c>
       <c r="L14" s="11"/>
-      <c r="M14" s="99"/>
+      <c r="M14" s="94"/>
       <c r="N14" s="9">
         <v>90</v>
       </c>
@@ -2118,28 +2078,28 @@
         <v>30</v>
       </c>
       <c r="B15" s="77" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="77" t="s">
+      <c r="D15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="77" t="s">
+      <c r="E15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="77">
+      <c r="F15" s="7">
         <v>20</v>
       </c>
-      <c r="G15" s="77">
+      <c r="G15" s="7">
         <f t="shared" ref="G15" si="4">F15*42</f>
         <v>840</v>
       </c>
-      <c r="H15" s="77">
-        <v>42</v>
-      </c>
-      <c r="I15" s="77">
+      <c r="H15" s="7">
+        <v>42</v>
+      </c>
+      <c r="I15" s="7">
         <v>2.87</v>
       </c>
       <c r="J15" s="9">
@@ -2151,7 +2111,7 @@
         <v>0.88153310104529625</v>
       </c>
       <c r="L15" s="11"/>
-      <c r="M15" s="99"/>
+      <c r="M15" s="94"/>
       <c r="N15" s="9">
         <v>108</v>
       </c>
@@ -2165,28 +2125,28 @@
         <v>30</v>
       </c>
       <c r="B16" s="77" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" s="85" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="77" t="s">
+      <c r="D16" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="77" t="s">
+      <c r="E16" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="77">
+      <c r="F16" s="7">
         <v>15</v>
       </c>
-      <c r="G16" s="77">
+      <c r="G16" s="7">
         <f>F16*42</f>
         <v>630</v>
       </c>
       <c r="H16" s="10">
         <v>42</v>
       </c>
-      <c r="I16" s="77">
+      <c r="I16" s="7">
         <v>3.1</v>
       </c>
       <c r="J16" s="9">
@@ -2198,7 +2158,7 @@
         <v>0.70967741935483852</v>
       </c>
       <c r="L16" s="11"/>
-      <c r="M16" s="99"/>
+      <c r="M16" s="94"/>
       <c r="N16" s="9">
         <v>79.5</v>
       </c>
@@ -2212,31 +2172,31 @@
         <v>30</v>
       </c>
       <c r="B17" s="77" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="85" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="77" t="s">
+      <c r="D17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="77" t="s">
+      <c r="E17" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="77">
+      <c r="F17" s="7">
         <v>15</v>
       </c>
-      <c r="G17" s="77">
+      <c r="G17" s="7">
         <f t="shared" ref="G17:G18" si="5">F17*42</f>
         <v>630</v>
       </c>
-      <c r="H17" s="77">
-        <v>42</v>
-      </c>
-      <c r="I17" s="77">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J17" s="83">
+      <c r="H17" s="10">
+        <v>42</v>
+      </c>
+      <c r="I17" s="7">
+        <v>3.1</v>
+      </c>
+      <c r="J17" s="31">
         <f>N17/F16</f>
         <v>4.6500000000000004</v>
       </c>
@@ -2244,9 +2204,9 @@
         <f>J17/I16-1</f>
         <v>0.5</v>
       </c>
-      <c r="L17" s="100"/>
-      <c r="M17" s="101"/>
-      <c r="N17" s="83">
+      <c r="L17" s="32"/>
+      <c r="M17" s="92"/>
+      <c r="N17" s="82">
         <v>69.75</v>
       </c>
       <c r="O17" s="11"/>
@@ -2259,42 +2219,42 @@
         <v>30</v>
       </c>
       <c r="B18" s="77" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="85" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="77" t="s">
+      <c r="D18" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="77" t="s">
+      <c r="E18" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="77">
+      <c r="F18" s="7">
         <v>15</v>
       </c>
-      <c r="G18" s="77">
+      <c r="G18" s="7">
         <f t="shared" si="5"/>
         <v>630</v>
       </c>
-      <c r="H18" s="77">
-        <v>43</v>
-      </c>
-      <c r="I18" s="77">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="J18" s="83">
+      <c r="H18" s="10">
+        <v>42</v>
+      </c>
+      <c r="I18" s="7">
+        <v>3.1</v>
+      </c>
+      <c r="J18" s="31">
         <f>N18/F17</f>
-        <v>4.7166666666666668</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="K18" s="75">
         <f>J17/I16-1</f>
         <v>0.5</v>
       </c>
-      <c r="L18" s="102"/>
-      <c r="M18" s="103"/>
-      <c r="N18" s="83">
-        <v>70.75</v>
+      <c r="L18" s="35"/>
+      <c r="M18" s="93"/>
+      <c r="N18" s="82">
+        <v>69.75</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="28" t="s">
@@ -2306,9 +2266,9 @@
         <v>30</v>
       </c>
       <c r="B19" s="77" t="s">
-        <v>117</v>
-      </c>
-      <c r="C19" s="85" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="30" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="13" t="s">
@@ -2327,8 +2287,8 @@
       <c r="H19" s="10">
         <v>42</v>
       </c>
-      <c r="I19" s="77">
-        <v>6.1</v>
+      <c r="I19" s="7">
+        <v>3.1</v>
       </c>
       <c r="J19" s="34">
         <f>N19/14</f>
@@ -2356,29 +2316,29 @@
       <c r="A20" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="82" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="85" t="s">
+      <c r="B20" s="81" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" s="77" t="s">
+      <c r="D20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="77">
+      <c r="F20" s="7">
         <v>20</v>
       </c>
-      <c r="G20" s="77">
+      <c r="G20" s="7">
         <f>F20*42</f>
         <v>840</v>
       </c>
       <c r="H20" s="10">
         <v>42</v>
       </c>
-      <c r="I20" s="77">
+      <c r="I20" s="7">
         <v>3.92</v>
       </c>
       <c r="J20" s="9">
@@ -2403,32 +2363,32 @@
       <c r="A21" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="82" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="85" t="s">
+      <c r="B21" s="81" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="77" t="s">
+      <c r="D21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="77">
+      <c r="F21" s="7">
         <v>20</v>
       </c>
-      <c r="G21" s="77">
+      <c r="G21" s="7">
         <f t="shared" ref="G21:G23" si="6">F21*42</f>
         <v>840</v>
       </c>
       <c r="H21" s="10">
         <v>42</v>
       </c>
-      <c r="I21" s="77">
-        <v>4.92</v>
-      </c>
-      <c r="J21" s="83">
+      <c r="I21" s="7">
+        <v>3.92</v>
+      </c>
+      <c r="J21" s="31">
         <f>N21/F$20</f>
         <v>5.6</v>
       </c>
@@ -2438,7 +2398,7 @@
       </c>
       <c r="L21" s="31"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="83">
+      <c r="N21" s="82">
         <v>112</v>
       </c>
       <c r="O21" s="11"/>
@@ -2450,34 +2410,34 @@
       <c r="A22" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="82" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="85" t="s">
+      <c r="B22" s="81" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="77" t="s">
+      <c r="D22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="77">
+      <c r="F22" s="7">
         <v>20</v>
       </c>
-      <c r="G22" s="77">
+      <c r="G22" s="7">
         <f t="shared" si="6"/>
         <v>840</v>
       </c>
-      <c r="H22" s="78">
-        <v>42</v>
-      </c>
-      <c r="I22" s="77">
-        <v>5.92</v>
-      </c>
-      <c r="J22" s="83">
+      <c r="H22" s="13">
+        <v>42</v>
+      </c>
+      <c r="I22" s="7">
+        <v>3.92</v>
+      </c>
+      <c r="J22" s="31">
         <f>N22/F$20</f>
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="K22" s="75">
         <f>J21/I20-1</f>
@@ -2485,7 +2445,9 @@
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="14"/>
-      <c r="N22" s="84"/>
+      <c r="N22" s="82">
+        <v>112</v>
+      </c>
       <c r="O22" s="11"/>
       <c r="P22" s="28" t="s">
         <v>32</v>
@@ -2495,30 +2457,30 @@
       <c r="A23" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="82" t="s">
-        <v>118</v>
-      </c>
-      <c r="C23" s="85" t="s">
+      <c r="B23" s="81" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="77" t="s">
+      <c r="D23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="77">
+      <c r="F23" s="7">
         <v>20</v>
       </c>
-      <c r="G23" s="77">
+      <c r="G23" s="7">
         <f t="shared" si="6"/>
         <v>840</v>
       </c>
-      <c r="H23" s="78">
-        <v>43</v>
-      </c>
-      <c r="I23" s="77">
-        <v>6.92</v>
+      <c r="H23" s="13">
+        <v>42</v>
+      </c>
+      <c r="I23" s="7">
+        <v>3.92</v>
       </c>
       <c r="J23" s="9">
         <f>N23/F$20</f>
@@ -2542,10 +2504,10 @@
       <c r="A24" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="82" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="85" t="s">
+      <c r="B24" s="81" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="30" t="s">
         <v>39</v>
       </c>
       <c r="D24" s="10" t="s">
@@ -2564,7 +2526,7 @@
       <c r="H24" s="10">
         <v>42</v>
       </c>
-      <c r="I24" s="77">
+      <c r="I24" s="7">
         <v>7.92</v>
       </c>
       <c r="J24" s="9">
@@ -2595,7 +2557,7 @@
       <c r="A25" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="80" t="s">
         <v>45</v>
       </c>
       <c r="C25" s="37" t="s">
@@ -2645,26 +2607,26 @@
       <c r="B26" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="77" t="s">
+      <c r="C26" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="77" t="s">
+      <c r="D26" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="77" t="s">
+      <c r="E26" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F26" s="77">
+      <c r="F26" s="7">
         <v>20</v>
       </c>
-      <c r="G26" s="77">
+      <c r="G26" s="7">
         <f>F26*42</f>
         <v>840</v>
       </c>
       <c r="H26" s="10">
         <v>42</v>
       </c>
-      <c r="I26" s="77">
+      <c r="I26" s="7">
         <v>3.76</v>
       </c>
       <c r="J26" s="9">
@@ -2692,26 +2654,26 @@
       <c r="B27" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="77" t="s">
+      <c r="C27" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="77" t="s">
+      <c r="D27" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="77" t="s">
+      <c r="E27" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="77">
+      <c r="F27" s="7">
         <v>20</v>
       </c>
-      <c r="G27" s="77">
+      <c r="G27" s="7">
         <f t="shared" ref="G27:G29" si="7">F27*42</f>
         <v>840</v>
       </c>
       <c r="H27" s="10">
         <v>42</v>
       </c>
-      <c r="I27" s="77">
+      <c r="I27" s="7">
         <v>3.76</v>
       </c>
       <c r="J27" s="9">
@@ -2739,26 +2701,26 @@
       <c r="B28" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="77" t="s">
+      <c r="C28" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="77" t="s">
+      <c r="D28" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="77" t="s">
+      <c r="E28" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="77">
+      <c r="F28" s="7">
         <v>20</v>
       </c>
-      <c r="G28" s="77">
+      <c r="G28" s="7">
         <f t="shared" si="7"/>
         <v>840</v>
       </c>
       <c r="H28" s="10">
         <v>42</v>
       </c>
-      <c r="I28" s="77">
+      <c r="I28" s="7">
         <v>3.76</v>
       </c>
       <c r="J28" s="9">
@@ -2786,26 +2748,26 @@
       <c r="B29" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="77" t="s">
+      <c r="C29" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="77" t="s">
+      <c r="D29" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="77" t="s">
+      <c r="E29" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F29" s="77">
+      <c r="F29" s="7">
         <v>20</v>
       </c>
-      <c r="G29" s="77">
+      <c r="G29" s="7">
         <f t="shared" si="7"/>
         <v>840</v>
       </c>
       <c r="H29" s="10">
         <v>42</v>
       </c>
-      <c r="I29" s="77">
+      <c r="I29" s="7">
         <v>3.76</v>
       </c>
       <c r="J29" s="9">
@@ -2830,29 +2792,29 @@
       <c r="A30" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="90" t="s">
+      <c r="B30" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="85" t="s">
+      <c r="C30" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="77" t="s">
+      <c r="D30" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="77" t="s">
+      <c r="E30" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="77">
+      <c r="F30" s="7">
         <v>20</v>
       </c>
-      <c r="G30" s="77">
+      <c r="G30" s="7">
         <f>F30*42</f>
         <v>840</v>
       </c>
       <c r="H30" s="14">
         <v>42</v>
       </c>
-      <c r="I30" s="77">
+      <c r="I30" s="7">
         <v>3.91</v>
       </c>
       <c r="J30" s="34">
@@ -2877,29 +2839,29 @@
       <c r="A31" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="90" t="s">
+      <c r="B31" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="85" t="s">
+      <c r="C31" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="77" t="s">
+      <c r="D31" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E31" s="77" t="s">
+      <c r="E31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F31" s="77">
+      <c r="F31" s="7">
         <v>20</v>
       </c>
-      <c r="G31" s="77">
+      <c r="G31" s="7">
         <f t="shared" ref="G31:G32" si="8">F31*42</f>
         <v>840</v>
       </c>
       <c r="H31" s="14">
         <v>42</v>
       </c>
-      <c r="I31" s="77">
+      <c r="I31" s="7">
         <v>3.91</v>
       </c>
       <c r="J31" s="34">
@@ -2924,29 +2886,29 @@
       <c r="A32" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="90" t="s">
+      <c r="B32" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="85" t="s">
+      <c r="C32" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D32" s="77" t="s">
+      <c r="D32" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="77" t="s">
+      <c r="E32" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="77">
+      <c r="F32" s="7">
         <v>20</v>
       </c>
-      <c r="G32" s="77">
+      <c r="G32" s="7">
         <f t="shared" si="8"/>
         <v>840</v>
       </c>
       <c r="H32" s="14">
         <v>42</v>
       </c>
-      <c r="I32" s="77">
+      <c r="I32" s="7">
         <v>3.91</v>
       </c>
       <c r="J32" s="34">
@@ -2971,29 +2933,29 @@
       <c r="A33" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="90" t="s">
+      <c r="B33" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="85" t="s">
+      <c r="C33" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D33" s="77" t="s">
+      <c r="D33" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="77" t="s">
+      <c r="E33" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F33" s="77">
+      <c r="F33" s="7">
         <v>20</v>
       </c>
-      <c r="G33" s="77">
+      <c r="G33" s="7">
         <f>F33*42</f>
         <v>840</v>
       </c>
       <c r="H33" s="14">
         <v>42</v>
       </c>
-      <c r="I33" s="77">
+      <c r="I33" s="7">
         <v>4.43</v>
       </c>
       <c r="J33" s="34">
@@ -3018,29 +2980,29 @@
       <c r="A34" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="77" t="s">
+      <c r="D34" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="77" t="s">
+      <c r="E34" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F34" s="77">
+      <c r="F34" s="7">
         <v>20</v>
       </c>
-      <c r="G34" s="77">
+      <c r="G34" s="7">
         <f t="shared" ref="G34:G35" si="9">F34*42</f>
         <v>840</v>
       </c>
       <c r="H34" s="14">
         <v>42</v>
       </c>
-      <c r="I34" s="77">
+      <c r="I34" s="7">
         <v>4.43</v>
       </c>
       <c r="J34" s="34">
@@ -3065,29 +3027,29 @@
       <c r="A35" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="90" t="s">
+      <c r="B35" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="85" t="s">
+      <c r="C35" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="77" t="s">
+      <c r="D35" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="77" t="s">
+      <c r="E35" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F35" s="77">
+      <c r="F35" s="7">
         <v>20</v>
       </c>
-      <c r="G35" s="77">
+      <c r="G35" s="7">
         <f t="shared" si="9"/>
         <v>840</v>
       </c>
       <c r="H35" s="14">
         <v>42</v>
       </c>
-      <c r="I35" s="77">
+      <c r="I35" s="7">
         <v>4.43</v>
       </c>
       <c r="J35" s="34">
@@ -3109,10 +3071,10 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A36" s="82" t="s">
+      <c r="A36" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="87" t="s">
+      <c r="B36" s="83" t="s">
         <v>54</v>
       </c>
       <c r="C36" s="10" t="s">
@@ -3159,8 +3121,10 @@
       </c>
     </row>
     <row r="37" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A37" s="82"/>
-      <c r="B37" s="87" t="s">
+      <c r="A37" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="83" t="s">
         <v>57</v>
       </c>
       <c r="C37" s="10" t="s">
@@ -3210,29 +3174,29 @@
       <c r="A38" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="88" t="s">
+      <c r="B38" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="77" t="s">
+      <c r="C38" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="92" t="s">
+      <c r="D38" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="E38" s="77" t="s">
+      <c r="E38" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F38" s="77">
+      <c r="F38" s="7">
         <v>30</v>
       </c>
-      <c r="G38" s="77">
+      <c r="G38" s="7">
         <f>F38*42</f>
         <v>1260</v>
       </c>
       <c r="H38" s="10">
         <v>42</v>
       </c>
-      <c r="I38" s="77">
+      <c r="I38" s="7">
         <v>4.84</v>
       </c>
       <c r="J38" s="9">
@@ -3257,29 +3221,29 @@
       <c r="A39" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="88" t="s">
+      <c r="B39" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="77" t="s">
+      <c r="C39" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="92" t="s">
+      <c r="D39" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="E39" s="77" t="s">
+      <c r="E39" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F39" s="77">
+      <c r="F39" s="7">
         <v>30</v>
       </c>
-      <c r="G39" s="77">
+      <c r="G39" s="7">
         <f>F39*42</f>
         <v>1260</v>
       </c>
       <c r="H39" s="10">
         <v>42</v>
       </c>
-      <c r="I39" s="77">
+      <c r="I39" s="7">
         <v>4.84</v>
       </c>
       <c r="J39" s="9">
@@ -3304,7 +3268,7 @@
       <c r="A40" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="84" t="s">
         <v>63</v>
       </c>
       <c r="C40" s="7" t="s">
@@ -3358,7 +3322,7 @@
       <c r="A41" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B41" s="93" t="s">
+      <c r="B41" s="88" t="s">
         <v>66</v>
       </c>
       <c r="C41" s="48" t="s">
@@ -3380,13 +3344,13 @@
       <c r="H41" s="50">
         <v>42</v>
       </c>
-      <c r="I41" s="77" t="s">
+      <c r="I41" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J41" s="51">
         <v>5.15</v>
       </c>
-      <c r="K41" s="77" t="s">
+      <c r="K41" s="7" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="51"/>
@@ -3401,7 +3365,7 @@
       <c r="A42" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="89" t="s">
+      <c r="B42" s="85" t="s">
         <v>68</v>
       </c>
       <c r="C42" s="54" t="s">
@@ -3423,11 +3387,11 @@
       <c r="H42" s="54">
         <v>42</v>
       </c>
-      <c r="I42" s="77" t="s">
+      <c r="I42" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J42" s="57"/>
-      <c r="K42" s="77" t="s">
+      <c r="K42" s="7" t="s">
         <v>34</v>
       </c>
       <c r="L42" s="57"/>
@@ -3440,10 +3404,10 @@
       <c r="A43" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="81" t="s">
+      <c r="B43" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="85" t="s">
+      <c r="C43" s="30" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="10" t="s">
@@ -3485,21 +3449,21 @@
         <v>30</v>
       </c>
       <c r="P43" s="59" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="31.5">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="15.75">
       <c r="A44" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="81" t="s">
+      <c r="B44" s="80" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" s="16" t="s">
         <v>75</v>
-      </c>
-      <c r="C44" s="85" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>76</v>
       </c>
       <c r="E44" s="60">
         <v>1.1000000000000001</v>
@@ -3538,21 +3502,21 @@
         <v>45</v>
       </c>
       <c r="P44" s="61" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
       <c r="A45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" s="87" t="s">
         <v>77</v>
-      </c>
-      <c r="B45" s="91" t="s">
-        <v>78</v>
       </c>
       <c r="C45" s="30" t="s">
         <v>15</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E45" s="17">
         <v>0.875</v>
@@ -3596,16 +3560,16 @@
     </row>
     <row r="46" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B46" s="91" t="s">
-        <v>80</v>
+        <v>76</v>
+      </c>
+      <c r="B46" s="87" t="s">
+        <v>79</v>
       </c>
       <c r="C46" s="30" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E46" s="17">
         <v>0.75</v>
@@ -3648,16 +3612,16 @@
     </row>
     <row r="47" spans="1:16" s="64" customFormat="1" ht="18" customHeight="1">
       <c r="A47" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="87" t="s">
         <v>82</v>
-      </c>
-      <c r="B47" s="91" t="s">
-        <v>83</v>
       </c>
       <c r="C47" s="30" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E47" s="66"/>
       <c r="F47" s="67"/>
@@ -3665,7 +3629,7 @@
       <c r="H47" s="67"/>
       <c r="I47" s="67"/>
       <c r="J47" s="68"/>
-      <c r="K47" s="77" t="s">
+      <c r="K47" s="7" t="s">
         <v>34</v>
       </c>
       <c r="L47" s="68"/>
@@ -3676,16 +3640,16 @@
     </row>
     <row r="48" spans="1:16" s="64" customFormat="1" ht="19.5" customHeight="1">
       <c r="A48" s="77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="B48" s="94" t="s">
+      <c r="C48" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C48" s="77" t="s">
+      <c r="D48" s="70" t="s">
         <v>87</v>
-      </c>
-      <c r="D48" s="70" t="s">
-        <v>88</v>
       </c>
       <c r="E48" s="70">
         <v>5</v>
@@ -3721,21 +3685,21 @@
       </c>
       <c r="O48" s="11"/>
       <c r="P48" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:16" s="64" customFormat="1" ht="21" customHeight="1">
       <c r="A49" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B49" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49" s="89" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="70" t="s">
         <v>90</v>
-      </c>
-      <c r="C49" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="D49" s="70" t="s">
-        <v>91</v>
       </c>
       <c r="E49" s="70">
         <v>5</v>
@@ -3771,21 +3735,21 @@
       </c>
       <c r="O49" s="11"/>
       <c r="P49" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:16" s="64" customFormat="1" ht="21" customHeight="1">
       <c r="A50" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B50" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" s="89" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" s="70" t="s">
         <v>92</v>
-      </c>
-      <c r="C50" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="D50" s="70" t="s">
-        <v>93</v>
       </c>
       <c r="E50" s="70">
         <v>5</v>
@@ -3821,21 +3785,21 @@
       </c>
       <c r="O50" s="11"/>
       <c r="P50" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:16" s="64" customFormat="1" ht="18" customHeight="1">
       <c r="A51" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B51" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="89" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="70" t="s">
         <v>94</v>
-      </c>
-      <c r="C51" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="D51" s="70" t="s">
-        <v>95</v>
       </c>
       <c r="E51" s="70">
         <v>5</v>
@@ -3850,13 +3814,13 @@
       <c r="H51" s="10">
         <v>42</v>
       </c>
-      <c r="I51" s="77" t="s">
+      <c r="I51" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J51" s="9">
         <v>5.2</v>
       </c>
-      <c r="K51" s="77" t="s">
+      <c r="K51" s="7" t="s">
         <v>34</v>
       </c>
       <c r="L51" s="9">
@@ -3870,21 +3834,21 @@
       </c>
       <c r="O51" s="11"/>
       <c r="P51" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:16" s="64" customFormat="1" ht="22.5" customHeight="1">
       <c r="A52" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B52" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="89" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D52" s="70" t="s">
         <v>96</v>
-      </c>
-      <c r="C52" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="D52" s="70" t="s">
-        <v>97</v>
       </c>
       <c r="E52" s="70">
         <v>5</v>
@@ -3920,21 +3884,21 @@
       </c>
       <c r="O52" s="11"/>
       <c r="P52" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:16" s="64" customFormat="1" ht="20.25" customHeight="1">
       <c r="A53" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B53" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="89" t="s">
+        <v>97</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" s="70" t="s">
         <v>98</v>
-      </c>
-      <c r="C53" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="D53" s="70" t="s">
-        <v>99</v>
       </c>
       <c r="E53" s="70">
         <v>5</v>
@@ -3970,21 +3934,21 @@
       </c>
       <c r="O53" s="11"/>
       <c r="P53" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:16" s="64" customFormat="1" ht="18" customHeight="1">
       <c r="A54" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B54" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" s="89" t="s">
+        <v>99</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="70" t="s">
         <v>100</v>
-      </c>
-      <c r="C54" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="D54" s="70" t="s">
-        <v>101</v>
       </c>
       <c r="E54" s="70">
         <v>5</v>
@@ -4020,21 +3984,21 @@
       </c>
       <c r="O54" s="11"/>
       <c r="P54" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:16" s="64" customFormat="1" ht="19.5" customHeight="1">
       <c r="A55" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B55" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="89" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55" s="70" t="s">
         <v>102</v>
-      </c>
-      <c r="C55" s="85" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" s="70" t="s">
-        <v>103</v>
       </c>
       <c r="E55" s="70">
         <v>5</v>
@@ -4070,21 +4034,21 @@
       </c>
       <c r="O55" s="11"/>
       <c r="P55" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:16" s="64" customFormat="1" ht="19.5" customHeight="1">
       <c r="A56" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B56" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" s="89" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" s="70" t="s">
         <v>104</v>
-      </c>
-      <c r="C56" s="85" t="s">
-        <v>119</v>
-      </c>
-      <c r="D56" s="70" t="s">
-        <v>105</v>
       </c>
       <c r="E56" s="70">
         <v>5</v>
@@ -4120,21 +4084,21 @@
       </c>
       <c r="O56" s="11"/>
       <c r="P56" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:16" s="64" customFormat="1" ht="19.5" customHeight="1">
       <c r="A57" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B57" s="95" t="s">
+        <v>84</v>
+      </c>
+      <c r="B57" s="90" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" s="70" t="s">
         <v>106</v>
-      </c>
-      <c r="C57" s="85" t="s">
-        <v>119</v>
-      </c>
-      <c r="D57" s="70" t="s">
-        <v>107</v>
       </c>
       <c r="E57" s="70">
         <v>5</v>
@@ -4149,14 +4113,14 @@
       <c r="H57" s="10">
         <v>42</v>
       </c>
-      <c r="I57" s="77" t="s">
+      <c r="I57" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J57" s="9">
         <f>N57/40</f>
         <v>7.5</v>
       </c>
-      <c r="K57" s="77" t="s">
+      <c r="K57" s="7" t="s">
         <v>34</v>
       </c>
       <c r="L57" s="9">
@@ -4172,18 +4136,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:16" s="72" customFormat="1" ht="26.25" customHeight="1">
+    <row r="58" spans="1:16" s="72" customFormat="1" ht="21">
       <c r="A58" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B58" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B58" s="89" t="s">
+        <v>107</v>
+      </c>
+      <c r="C58" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="C58" s="85" t="s">
+      <c r="D58" s="70" t="s">
         <v>109</v>
-      </c>
-      <c r="D58" s="70" t="s">
-        <v>110</v>
       </c>
       <c r="E58" s="70">
         <v>5</v>
@@ -4219,19 +4183,19 @@
       </c>
       <c r="O58" s="11"/>
       <c r="P58" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:16" s="64" customFormat="1" ht="19.5" customHeight="1">
       <c r="A59" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B59" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" s="89" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" s="96"/>
+      <c r="D59" s="70" t="s">
         <v>111</v>
-      </c>
-      <c r="C59" s="86"/>
-      <c r="D59" s="70" t="s">
-        <v>112</v>
       </c>
       <c r="E59" s="70">
         <v>5</v>
@@ -4246,13 +4210,13 @@
       <c r="H59" s="10">
         <v>42</v>
       </c>
-      <c r="I59" s="77" t="s">
+      <c r="I59" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J59" s="9">
         <v>4</v>
       </c>
-      <c r="K59" s="77" t="s">
+      <c r="K59" s="7" t="s">
         <v>34</v>
       </c>
       <c r="L59" s="9">
@@ -4266,7 +4230,7 @@
       </c>
       <c r="O59" s="11"/>
       <c r="P59" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Products Price table Web.xlsx
+++ b/Products Price table Web.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6622B38C-84F4-45E0-BB73-C53FDF1BF103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF8B168-99EF-44BE-A94D-5A8A069D13AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
   </bookViews>
   <sheets>
     <sheet name="Item Classification 7.14.26" sheetId="1" r:id="rId1"/>
@@ -3100,20 +3100,20 @@
         <v>4.92</v>
       </c>
       <c r="J36" s="9">
-        <f>N36/F36</f>
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="K36" s="75">
         <f t="shared" si="1"/>
-        <v>0.19918699186991873</v>
+        <v>0.32113821138211374</v>
       </c>
       <c r="L36" s="9">
         <f>N36/8</f>
-        <v>29.5</v>
+        <v>32.5</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="9">
-        <v>236</v>
+        <f>J36*F36</f>
+        <v>260</v>
       </c>
       <c r="O36" s="11"/>
       <c r="P36" s="41" t="s">
@@ -3150,20 +3150,20 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="J37" s="9">
-        <f>N37/F37</f>
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="K37" s="75">
         <f t="shared" si="1"/>
-        <v>0.24735729386892169</v>
+        <v>0.37420718816067633</v>
       </c>
       <c r="L37" s="9">
         <f>N37/8</f>
-        <v>29.5</v>
+        <v>32.5</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="9">
-        <v>236</v>
+        <f>J37*F37</f>
+        <v>260</v>
       </c>
       <c r="O37" s="11"/>
       <c r="P37" s="41" t="s">
@@ -3452,7 +3452,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="15.75">
+    <row r="44" spans="1:16" ht="31.5">
       <c r="A44" s="77" t="s">
         <v>70</v>
       </c>

--- a/Products Price table Web.xlsx
+++ b/Products Price table Web.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF8B168-99EF-44BE-A94D-5A8A069D13AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327DB224-D862-4E50-BF0E-85D55B4E9854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
   </bookViews>
   <sheets>
     <sheet name="Item Classification 7.14.26" sheetId="1" r:id="rId1"/>
@@ -3867,20 +3867,20 @@
         <v>2.75</v>
       </c>
       <c r="J52" s="9">
-        <v>2.95</v>
+        <v>3.88</v>
       </c>
       <c r="K52" s="75">
         <f t="shared" si="1"/>
-        <v>7.2727272727272751E-2</v>
+        <v>0.41090909090909089</v>
       </c>
       <c r="L52" s="9">
         <f t="shared" si="12"/>
-        <v>14.75</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="9">
         <f t="shared" si="13"/>
-        <v>118</v>
+        <v>155.19999999999999</v>
       </c>
       <c r="O52" s="11"/>
       <c r="P52" s="71" t="s">
@@ -3917,20 +3917,20 @@
         <v>2.7</v>
       </c>
       <c r="J53" s="9">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="K53" s="75">
         <f t="shared" si="1"/>
-        <v>0.20370370370370372</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="L53" s="9">
         <f t="shared" si="12"/>
-        <v>16.25</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="9">
         <f t="shared" si="13"/>
-        <v>130</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="O53" s="11"/>
       <c r="P53" s="71" t="s">
@@ -3967,20 +3967,20 @@
         <v>2.58</v>
       </c>
       <c r="J54" s="9">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K54" s="75">
         <f t="shared" si="1"/>
-        <v>0.27906976744186029</v>
+        <v>0.41472868217054248</v>
       </c>
       <c r="L54" s="9">
         <f t="shared" si="12"/>
-        <v>16.5</v>
+        <v>18.25</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="9">
         <f t="shared" si="13"/>
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="O54" s="11"/>
       <c r="P54" s="71" t="s">

--- a/Products Price table Web.xlsx
+++ b/Products Price table Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327DB224-D862-4E50-BF0E-85D55B4E9854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3C9C01-ECAA-4C3E-95F1-B5D511D148E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
   </bookViews>
@@ -3867,20 +3867,20 @@
         <v>2.75</v>
       </c>
       <c r="J52" s="9">
-        <v>3.88</v>
+        <v>3.38</v>
       </c>
       <c r="K52" s="75">
         <f t="shared" si="1"/>
-        <v>0.41090909090909089</v>
+        <v>0.22909090909090901</v>
       </c>
       <c r="L52" s="9">
         <f t="shared" si="12"/>
-        <v>19.399999999999999</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="9">
         <f t="shared" si="13"/>
-        <v>155.19999999999999</v>
+        <v>135.19999999999999</v>
       </c>
       <c r="O52" s="11"/>
       <c r="P52" s="71" t="s">
